--- a/filer/41792019_bravo.xlsx
+++ b/filer/41792019_bravo.xlsx
@@ -613,7 +613,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/41792019_bravo.xlsx
+++ b/filer/41792019_bravo.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -603,11 +603,13 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -624,14 +626,16 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Indekstal (2021=100)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -651,18 +655,24 @@
       <c r="E3" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
+      <c r="F3" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="I3" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -687,21 +697,29 @@
         <f>'res_raw_41792019'!$E$2</f>
         <v/>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" s="6">
+      <c r="F4" s="5">
+        <f>'res_raw_41792019'!$F$2</f>
+        <v/>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="6">
         <f>IFERROR(B4/$B$4*100,"")</f>
         <v/>
       </c>
-      <c r="H4" s="6">
+      <c r="I4" s="6">
         <f>IFERROR(C4/$B$4*100,"")</f>
         <v/>
       </c>
-      <c r="I4" s="6">
+      <c r="J4" s="6">
         <f>IFERROR(D4/$B$4*100,"")</f>
         <v/>
       </c>
-      <c r="J4" s="6">
+      <c r="K4" s="6">
         <f>IFERROR(E4/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="6">
+        <f>IFERROR(F4/$B$4*100,"")</f>
         <v/>
       </c>
     </row>
@@ -727,21 +745,29 @@
         <f>'res_raw_41792019'!$E$3</f>
         <v/>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" s="9">
+      <c r="F5" s="8">
+        <f>'res_raw_41792019'!$F$3</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="9">
         <f>IFERROR(B5/$B$5*100,"")</f>
         <v/>
       </c>
-      <c r="H5" s="9">
+      <c r="I5" s="9">
         <f>IFERROR(C5/$B$5*100,"")</f>
         <v/>
       </c>
-      <c r="I5" s="9">
+      <c r="J5" s="9">
         <f>IFERROR(D5/$B$5*100,"")</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="K5" s="9">
         <f>IFERROR(E5/$B$5*100,"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="9">
+        <f>IFERROR(F5/$B$5*100,"")</f>
         <v/>
       </c>
     </row>
@@ -767,21 +793,29 @@
         <f>'res_raw_41792019'!$E$4</f>
         <v/>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" s="6">
+      <c r="F6" s="5">
+        <f>'res_raw_41792019'!$F$4</f>
+        <v/>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="6">
         <f>IFERROR(B6/$B$6*100,"")</f>
         <v/>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <f>IFERROR(C6/$B$6*100,"")</f>
         <v/>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6">
         <f>IFERROR(D6/$B$6*100,"")</f>
         <v/>
       </c>
-      <c r="J6" s="6">
+      <c r="K6" s="6">
         <f>IFERROR(E6/$B$6*100,"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="6">
+        <f>IFERROR(F6/$B$6*100,"")</f>
         <v/>
       </c>
     </row>
@@ -807,21 +841,29 @@
         <f>'res_raw_41792019'!$E$5</f>
         <v/>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" s="9">
+      <c r="F7" s="8">
+        <f>'res_raw_41792019'!$F$5</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="9">
         <f>IFERROR(B7/$B$7*100,"")</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="I7" s="9">
         <f>IFERROR(C7/$B$7*100,"")</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="J7" s="9">
         <f>IFERROR(D7/$B$7*100,"")</f>
         <v/>
       </c>
-      <c r="J7" s="9">
+      <c r="K7" s="9">
         <f>IFERROR(E7/$B$7*100,"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="9">
+        <f>IFERROR(F7/$B$7*100,"")</f>
         <v/>
       </c>
     </row>
@@ -847,21 +889,29 @@
         <f>'res_raw_41792019'!$E$6</f>
         <v/>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" s="12">
+      <c r="F8" s="11">
+        <f>'res_raw_41792019'!$F$6</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" s="12">
         <f>IFERROR(B8/$B$8*100,"")</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="I8" s="12">
         <f>IFERROR(C8/$B$8*100,"")</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="J8" s="12">
         <f>IFERROR(D8/$B$8*100,"")</f>
         <v/>
       </c>
-      <c r="J8" s="12">
+      <c r="K8" s="12">
         <f>IFERROR(E8/$B$8*100,"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>IFERROR(F8/$B$8*100,"")</f>
         <v/>
       </c>
     </row>
@@ -887,21 +937,29 @@
         <f>'res_raw_41792019'!$E$7</f>
         <v/>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" s="9">
+      <c r="F9" s="8">
+        <f>'res_raw_41792019'!$F$7</f>
+        <v/>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" s="9">
         <f>IFERROR(B9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="9">
         <f>IFERROR(C9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="J9" s="9">
         <f>IFERROR(D9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="J9" s="9">
+      <c r="K9" s="9">
         <f>IFERROR(E9/$B$9*100,"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="9">
+        <f>IFERROR(F9/$B$9*100,"")</f>
         <v/>
       </c>
     </row>
@@ -927,21 +985,29 @@
         <f>IFERROR($E$8-ABS($E$9),"")</f>
         <v/>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" s="12">
+      <c r="F10" s="11">
+        <f>IFERROR($F$8-ABS($F$9),"")</f>
+        <v/>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="12">
         <f>IFERROR(B10/$B$10*100,"")</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="I10" s="12">
         <f>IFERROR(C10/$B$10*100,"")</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="J10" s="12">
         <f>IFERROR(D10/$B$10*100,"")</f>
         <v/>
       </c>
-      <c r="J10" s="12">
+      <c r="K10" s="12">
         <f>IFERROR(E10/$B$10*100,"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="12">
+        <f>IFERROR(F10/$B$10*100,"")</f>
         <v/>
       </c>
     </row>
@@ -967,21 +1033,29 @@
         <f>'res_raw_41792019'!$E$9</f>
         <v/>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" s="9">
+      <c r="F11" s="8">
+        <f>'res_raw_41792019'!$F$9</f>
+        <v/>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="9">
         <f>IFERROR(B11/$B$11*100,"")</f>
         <v/>
       </c>
-      <c r="H11" s="9">
+      <c r="I11" s="9">
         <f>IFERROR(C11/$B$11*100,"")</f>
         <v/>
       </c>
-      <c r="I11" s="9">
+      <c r="J11" s="9">
         <f>IFERROR(D11/$B$11*100,"")</f>
         <v/>
       </c>
-      <c r="J11" s="9">
+      <c r="K11" s="9">
         <f>IFERROR(E11/$B$11*100,"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="9">
+        <f>IFERROR(F11/$B$11*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1007,21 +1081,29 @@
         <f>'res_raw_41792019'!$E$10</f>
         <v/>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" s="6">
+      <c r="F12" s="5">
+        <f>'res_raw_41792019'!$F$10</f>
+        <v/>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" s="6">
         <f>IFERROR(B12/$B$12*100,"")</f>
         <v/>
       </c>
-      <c r="H12" s="6">
+      <c r="I12" s="6">
         <f>IFERROR(C12/$B$12*100,"")</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="J12" s="6">
         <f>IFERROR(D12/$B$12*100,"")</f>
         <v/>
       </c>
-      <c r="J12" s="6">
+      <c r="K12" s="6">
         <f>IFERROR(E12/$B$12*100,"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="6">
+        <f>IFERROR(F12/$B$12*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1047,21 +1129,29 @@
         <f>'res_raw_41792019'!$E$11</f>
         <v/>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" s="12">
+      <c r="F13" s="11">
+        <f>'res_raw_41792019'!$F$11</f>
+        <v/>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" s="12">
         <f>IFERROR(B13/$B$13*100,"")</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="I13" s="12">
         <f>IFERROR(C13/$B$13*100,"")</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="J13" s="12">
         <f>IFERROR(D13/$B$13*100,"")</f>
         <v/>
       </c>
-      <c r="J13" s="12">
+      <c r="K13" s="12">
         <f>IFERROR(E13/$B$13*100,"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="12">
+        <f>IFERROR(F13/$B$13*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1087,21 +1177,29 @@
         <f>'res_raw_41792019'!$E$12</f>
         <v/>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" s="6">
+      <c r="F14" s="5">
+        <f>'res_raw_41792019'!$F$12</f>
+        <v/>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" s="6">
         <f>IFERROR(B14/$B$14*100,"")</f>
         <v/>
       </c>
-      <c r="H14" s="6">
+      <c r="I14" s="6">
         <f>IFERROR(C14/$B$14*100,"")</f>
         <v/>
       </c>
-      <c r="I14" s="6">
+      <c r="J14" s="6">
         <f>IFERROR(D14/$B$14*100,"")</f>
         <v/>
       </c>
-      <c r="J14" s="6">
+      <c r="K14" s="6">
         <f>IFERROR(E14/$B$14*100,"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="6">
+        <f>IFERROR(F14/$B$14*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1127,21 +1225,29 @@
         <f>'res_raw_41792019'!$E$13</f>
         <v/>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" s="9">
+      <c r="F15" s="8">
+        <f>'res_raw_41792019'!$F$13</f>
+        <v/>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" s="9">
         <f>IFERROR(B15/$B$15*100,"")</f>
         <v/>
       </c>
-      <c r="H15" s="9">
+      <c r="I15" s="9">
         <f>IFERROR(C15/$B$15*100,"")</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="J15" s="9">
         <f>IFERROR(D15/$B$15*100,"")</f>
         <v/>
       </c>
-      <c r="J15" s="9">
+      <c r="K15" s="9">
         <f>IFERROR(E15/$B$15*100,"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="9">
+        <f>IFERROR(F15/$B$15*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1167,21 +1273,29 @@
         <f>'res_raw_41792019'!$E$14</f>
         <v/>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" s="6">
+      <c r="F16" s="5">
+        <f>'res_raw_41792019'!$F$14</f>
+        <v/>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" s="6">
         <f>IFERROR(B16/$B$16*100,"")</f>
         <v/>
       </c>
-      <c r="H16" s="6">
+      <c r="I16" s="6">
         <f>IFERROR(C16/$B$16*100,"")</f>
         <v/>
       </c>
-      <c r="I16" s="6">
+      <c r="J16" s="6">
         <f>IFERROR(D16/$B$16*100,"")</f>
         <v/>
       </c>
-      <c r="J16" s="6">
+      <c r="K16" s="6">
         <f>IFERROR(E16/$B$16*100,"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="6">
+        <f>IFERROR(F16/$B$16*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1207,21 +1321,29 @@
         <f>'res_raw_41792019'!$E$15</f>
         <v/>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" s="12">
+      <c r="F17" s="11">
+        <f>'res_raw_41792019'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" s="12">
         <f>IFERROR(B17/$B$17*100,"")</f>
         <v/>
       </c>
-      <c r="H17" s="12">
+      <c r="I17" s="12">
         <f>IFERROR(C17/$B$17*100,"")</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="J17" s="12">
         <f>IFERROR(D17/$B$17*100,"")</f>
         <v/>
       </c>
-      <c r="J17" s="12">
+      <c r="K17" s="12">
         <f>IFERROR(E17/$B$17*100,"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="12">
+        <f>IFERROR(F17/$B$17*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1247,21 +1369,29 @@
         <f>'res_raw_41792019'!$E$16</f>
         <v/>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" s="12">
+      <c r="F18" s="11">
+        <f>'res_raw_41792019'!$F$16</f>
+        <v/>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="12">
         <f>IFERROR(B18/$B$18*100,"")</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="I18" s="12">
         <f>IFERROR(C18/$B$18*100,"")</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="J18" s="12">
         <f>IFERROR(D18/$B$18*100,"")</f>
         <v/>
       </c>
-      <c r="J18" s="12">
+      <c r="K18" s="12">
         <f>IFERROR(E18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="12">
+        <f>IFERROR(F18/$B$18*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1287,21 +1417,29 @@
         <f>'res_raw_41792019'!$E$17</f>
         <v/>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" s="9">
+      <c r="F19" s="8">
+        <f>'res_raw_41792019'!$F$17</f>
+        <v/>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" s="9">
         <f>IFERROR(B19/$B$19*100,"")</f>
         <v/>
       </c>
-      <c r="H19" s="9">
+      <c r="I19" s="9">
         <f>IFERROR(C19/$B$19*100,"")</f>
         <v/>
       </c>
-      <c r="I19" s="9">
+      <c r="J19" s="9">
         <f>IFERROR(D19/$B$19*100,"")</f>
         <v/>
       </c>
-      <c r="J19" s="9">
+      <c r="K19" s="9">
         <f>IFERROR(E19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="9">
+        <f>IFERROR(F19/$B$19*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1327,21 +1465,29 @@
         <f>'res_raw_41792019'!$E$18</f>
         <v/>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" s="12">
+      <c r="F20" s="11">
+        <f>'res_raw_41792019'!$F$18</f>
+        <v/>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="12">
         <f>IFERROR(B20/$B$20*100,"")</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="I20" s="12">
         <f>IFERROR(C20/$B$20*100,"")</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="J20" s="12">
         <f>IFERROR(D20/$B$20*100,"")</f>
         <v/>
       </c>
-      <c r="J20" s="12">
+      <c r="K20" s="12">
         <f>IFERROR(E20/$B$20*100,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="12">
+        <f>IFERROR(F20/$B$20*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1363,18 +1509,24 @@
       <c r="E22" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" s="3" t="n">
+      <c r="F22" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="I22" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="J22" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="K22" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -1399,21 +1551,29 @@
         <f>'balance_raw_41792019'!$E$2</f>
         <v/>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" s="9">
+      <c r="F23" s="8">
+        <f>'balance_raw_41792019'!$F$2</f>
+        <v/>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" s="9">
         <f>IFERROR(B23/$B$23*100,"")</f>
         <v/>
       </c>
-      <c r="H23" s="9">
+      <c r="I23" s="9">
         <f>IFERROR(C23/$B$23*100,"")</f>
         <v/>
       </c>
-      <c r="I23" s="9">
+      <c r="J23" s="9">
         <f>IFERROR(D23/$B$23*100,"")</f>
         <v/>
       </c>
-      <c r="J23" s="9">
+      <c r="K23" s="9">
         <f>IFERROR(E23/$B$23*100,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="9">
+        <f>IFERROR(F23/$B$23*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1439,21 +1599,29 @@
         <f>'balance_raw_41792019'!$E$3</f>
         <v/>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" s="6">
+      <c r="F24" s="5">
+        <f>'balance_raw_41792019'!$F$3</f>
+        <v/>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" s="6">
         <f>IFERROR(B24/$B$24*100,"")</f>
         <v/>
       </c>
-      <c r="H24" s="6">
+      <c r="I24" s="6">
         <f>IFERROR(C24/$B$24*100,"")</f>
         <v/>
       </c>
-      <c r="I24" s="6">
+      <c r="J24" s="6">
         <f>IFERROR(D24/$B$24*100,"")</f>
         <v/>
       </c>
-      <c r="J24" s="6">
+      <c r="K24" s="6">
         <f>IFERROR(E24/$B$24*100,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="6">
+        <f>IFERROR(F24/$B$24*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1479,21 +1647,29 @@
         <f>'balance_raw_41792019'!$E$4</f>
         <v/>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" s="9">
+      <c r="F25" s="8">
+        <f>'balance_raw_41792019'!$F$4</f>
+        <v/>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="9">
         <f>IFERROR(B25/$B$25*100,"")</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="I25" s="9">
         <f>IFERROR(C25/$B$25*100,"")</f>
         <v/>
       </c>
-      <c r="I25" s="9">
+      <c r="J25" s="9">
         <f>IFERROR(D25/$B$25*100,"")</f>
         <v/>
       </c>
-      <c r="J25" s="9">
+      <c r="K25" s="9">
         <f>IFERROR(E25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="9">
+        <f>IFERROR(F25/$B$25*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1519,21 +1695,29 @@
         <f>'balance_raw_41792019'!$E$5</f>
         <v/>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" s="12">
+      <c r="F26" s="11">
+        <f>'balance_raw_41792019'!$F$5</f>
+        <v/>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="12">
         <f>IFERROR(B26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="H26" s="12">
+      <c r="I26" s="12">
         <f>IFERROR(C26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="I26" s="12">
+      <c r="J26" s="12">
         <f>IFERROR(D26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="J26" s="12">
+      <c r="K26" s="12">
         <f>IFERROR(E26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="12">
+        <f>IFERROR(F26/$B$26*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1559,21 +1743,29 @@
         <f>'balance_raw_41792019'!$E$6</f>
         <v/>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" s="9">
+      <c r="F27" s="8">
+        <f>'balance_raw_41792019'!$F$6</f>
+        <v/>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" s="9">
         <f>IFERROR(B27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="I27" s="9">
         <f>IFERROR(C27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="I27" s="9">
+      <c r="J27" s="9">
         <f>IFERROR(D27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="J27" s="9">
+      <c r="K27" s="9">
         <f>IFERROR(E27/$B$27*100,"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="9">
+        <f>IFERROR(F27/$B$27*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1599,21 +1791,29 @@
         <f>'balance_raw_41792019'!$E$7</f>
         <v/>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" s="6">
+      <c r="F28" s="5">
+        <f>'balance_raw_41792019'!$F$7</f>
+        <v/>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" s="6">
         <f>IFERROR(B28/$B$28*100,"")</f>
         <v/>
       </c>
-      <c r="H28" s="6">
+      <c r="I28" s="6">
         <f>IFERROR(C28/$B$28*100,"")</f>
         <v/>
       </c>
-      <c r="I28" s="6">
+      <c r="J28" s="6">
         <f>IFERROR(D28/$B$28*100,"")</f>
         <v/>
       </c>
-      <c r="J28" s="6">
+      <c r="K28" s="6">
         <f>IFERROR(E28/$B$28*100,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="6">
+        <f>IFERROR(F28/$B$28*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1639,21 +1839,29 @@
         <f>'balance_raw_41792019'!$E$8</f>
         <v/>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" s="9">
+      <c r="F29" s="8">
+        <f>'balance_raw_41792019'!$F$8</f>
+        <v/>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" s="9">
         <f>IFERROR(B29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="H29" s="9">
+      <c r="I29" s="9">
         <f>IFERROR(C29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="J29" s="9">
         <f>IFERROR(D29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="J29" s="9">
+      <c r="K29" s="9">
         <f>IFERROR(E29/$B$29*100,"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="9">
+        <f>IFERROR(F29/$B$29*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1679,21 +1887,29 @@
         <f>'balance_raw_41792019'!$E$9</f>
         <v/>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" s="6">
+      <c r="F30" s="5">
+        <f>'balance_raw_41792019'!$F$9</f>
+        <v/>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" s="6">
         <f>IFERROR(B30/$B$30*100,"")</f>
         <v/>
       </c>
-      <c r="H30" s="6">
+      <c r="I30" s="6">
         <f>IFERROR(C30/$B$30*100,"")</f>
         <v/>
       </c>
-      <c r="I30" s="6">
+      <c r="J30" s="6">
         <f>IFERROR(D30/$B$30*100,"")</f>
         <v/>
       </c>
-      <c r="J30" s="6">
+      <c r="K30" s="6">
         <f>IFERROR(E30/$B$30*100,"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="6">
+        <f>IFERROR(F30/$B$30*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1719,21 +1935,29 @@
         <f>'balance_raw_41792019'!$E$10</f>
         <v/>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" s="9">
+      <c r="F31" s="8">
+        <f>'balance_raw_41792019'!$F$10</f>
+        <v/>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" s="9">
         <f>IFERROR(B31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="H31" s="9">
+      <c r="I31" s="9">
         <f>IFERROR(C31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="I31" s="9">
+      <c r="J31" s="9">
         <f>IFERROR(D31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="J31" s="9">
+      <c r="K31" s="9">
         <f>IFERROR(E31/$B$31*100,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="9">
+        <f>IFERROR(F31/$B$31*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1759,21 +1983,29 @@
         <f>'balance_raw_41792019'!$E$11</f>
         <v/>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" s="12">
+      <c r="F32" s="11">
+        <f>'balance_raw_41792019'!$F$11</f>
+        <v/>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" s="12">
         <f>IFERROR(B32/$B$32*100,"")</f>
         <v/>
       </c>
-      <c r="H32" s="12">
+      <c r="I32" s="12">
         <f>IFERROR(C32/$B$32*100,"")</f>
         <v/>
       </c>
-      <c r="I32" s="12">
+      <c r="J32" s="12">
         <f>IFERROR(D32/$B$32*100,"")</f>
         <v/>
       </c>
-      <c r="J32" s="12">
+      <c r="K32" s="12">
         <f>IFERROR(E32/$B$32*100,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="12">
+        <f>IFERROR(F32/$B$32*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1799,21 +2031,29 @@
         <f>'balance_raw_41792019'!$E$12</f>
         <v/>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" s="9">
+      <c r="F33" s="8">
+        <f>'balance_raw_41792019'!$F$12</f>
+        <v/>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" s="9">
         <f>IFERROR(B33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="H33" s="9">
+      <c r="I33" s="9">
         <f>IFERROR(C33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="I33" s="9">
+      <c r="J33" s="9">
         <f>IFERROR(D33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="J33" s="9">
+      <c r="K33" s="9">
         <f>IFERROR(E33/$B$33*100,"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="9">
+        <f>IFERROR(F33/$B$33*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1839,21 +2079,29 @@
         <f>'balance_raw_41792019'!$E$13</f>
         <v/>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" s="6">
+      <c r="F34" s="5">
+        <f>'balance_raw_41792019'!$F$13</f>
+        <v/>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" s="6">
         <f>IFERROR(B34/$B$34*100,"")</f>
         <v/>
       </c>
-      <c r="H34" s="6">
+      <c r="I34" s="6">
         <f>IFERROR(C34/$B$34*100,"")</f>
         <v/>
       </c>
-      <c r="I34" s="6">
+      <c r="J34" s="6">
         <f>IFERROR(D34/$B$34*100,"")</f>
         <v/>
       </c>
-      <c r="J34" s="6">
+      <c r="K34" s="6">
         <f>IFERROR(E34/$B$34*100,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="6">
+        <f>IFERROR(F34/$B$34*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1879,21 +2127,29 @@
         <f>'balance_raw_41792019'!$E$14</f>
         <v/>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" s="12">
+      <c r="F35" s="11">
+        <f>'balance_raw_41792019'!$F$14</f>
+        <v/>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" s="12">
         <f>IFERROR(B35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="H35" s="12">
+      <c r="I35" s="12">
         <f>IFERROR(C35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="I35" s="12">
+      <c r="J35" s="12">
         <f>IFERROR(D35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="J35" s="12">
+      <c r="K35" s="12">
         <f>IFERROR(E35/$B$35*100,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="12">
+        <f>IFERROR(F35/$B$35*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1919,21 +2175,29 @@
         <f>'balance_raw_41792019'!$E$15</f>
         <v/>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" s="12">
+      <c r="F36" s="11">
+        <f>'balance_raw_41792019'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" s="12">
         <f>IFERROR(B36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="H36" s="12">
+      <c r="I36" s="12">
         <f>IFERROR(C36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="I36" s="12">
+      <c r="J36" s="12">
         <f>IFERROR(D36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="J36" s="12">
+      <c r="K36" s="12">
         <f>IFERROR(E36/$B$36*100,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="12">
+        <f>IFERROR(F36/$B$36*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1959,21 +2223,29 @@
         <f>'balance_raw_41792019'!$E$16</f>
         <v/>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" s="9">
+      <c r="F37" s="8">
+        <f>'balance_raw_41792019'!$F$16</f>
+        <v/>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" s="9">
         <f>IFERROR(B37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="H37" s="9">
+      <c r="I37" s="9">
         <f>IFERROR(C37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="I37" s="9">
+      <c r="J37" s="9">
         <f>IFERROR(D37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="J37" s="9">
+      <c r="K37" s="9">
         <f>IFERROR(E37/$B$37*100,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="9">
+        <f>IFERROR(F37/$B$37*100,"")</f>
         <v/>
       </c>
     </row>
@@ -1999,21 +2271,29 @@
         <f>'balance_raw_41792019'!$E$17</f>
         <v/>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" s="6">
+      <c r="F38" s="5">
+        <f>'balance_raw_41792019'!$F$17</f>
+        <v/>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" s="6">
         <f>IFERROR(B38/$B$38*100,"")</f>
         <v/>
       </c>
-      <c r="H38" s="6">
+      <c r="I38" s="6">
         <f>IFERROR(C38/$B$38*100,"")</f>
         <v/>
       </c>
-      <c r="I38" s="6">
+      <c r="J38" s="6">
         <f>IFERROR(D38/$B$38*100,"")</f>
         <v/>
       </c>
-      <c r="J38" s="6">
+      <c r="K38" s="6">
         <f>IFERROR(E38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>IFERROR(F38/$B$38*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2039,21 +2319,29 @@
         <f>'balance_raw_41792019'!$E$18</f>
         <v/>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" s="9">
+      <c r="F39" s="8">
+        <f>'balance_raw_41792019'!$F$18</f>
+        <v/>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" s="9">
         <f>IFERROR(B39/$B$39*100,"")</f>
         <v/>
       </c>
-      <c r="H39" s="9">
+      <c r="I39" s="9">
         <f>IFERROR(C39/$B$39*100,"")</f>
         <v/>
       </c>
-      <c r="I39" s="9">
+      <c r="J39" s="9">
         <f>IFERROR(D39/$B$39*100,"")</f>
         <v/>
       </c>
-      <c r="J39" s="9">
+      <c r="K39" s="9">
         <f>IFERROR(E39/$B$39*100,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="9">
+        <f>IFERROR(F39/$B$39*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2079,21 +2367,29 @@
         <f>'balance_raw_41792019'!$E$19</f>
         <v/>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" s="6">
+      <c r="F40" s="5">
+        <f>'balance_raw_41792019'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" s="6">
         <f>IFERROR(B40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="H40" s="6">
+      <c r="I40" s="6">
         <f>IFERROR(C40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="I40" s="6">
+      <c r="J40" s="6">
         <f>IFERROR(D40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="J40" s="6">
+      <c r="K40" s="6">
         <f>IFERROR(E40/$B$40*100,"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="6">
+        <f>IFERROR(F40/$B$40*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2119,21 +2415,29 @@
         <f>'balance_raw_41792019'!$E$20</f>
         <v/>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" s="9">
+      <c r="F41" s="8">
+        <f>'balance_raw_41792019'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" s="9">
         <f>IFERROR(B41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="H41" s="9">
+      <c r="I41" s="9">
         <f>IFERROR(C41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="I41" s="9">
+      <c r="J41" s="9">
         <f>IFERROR(D41/$B$41*100,"")</f>
         <v/>
       </c>
-      <c r="J41" s="9">
+      <c r="K41" s="9">
         <f>IFERROR(E41/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="9">
+        <f>IFERROR(F41/$B$41*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2159,21 +2463,29 @@
         <f>'balance_raw_41792019'!$E$21</f>
         <v/>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" s="6">
+      <c r="F42" s="5">
+        <f>'balance_raw_41792019'!$F$21</f>
+        <v/>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" s="6">
         <f>IFERROR(B42/$B$42*100,"")</f>
         <v/>
       </c>
-      <c r="H42" s="6">
+      <c r="I42" s="6">
         <f>IFERROR(C42/$B$42*100,"")</f>
         <v/>
       </c>
-      <c r="I42" s="6">
+      <c r="J42" s="6">
         <f>IFERROR(D42/$B$42*100,"")</f>
         <v/>
       </c>
-      <c r="J42" s="6">
+      <c r="K42" s="6">
         <f>IFERROR(E42/$B$42*100,"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="6">
+        <f>IFERROR(F42/$B$42*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2199,21 +2511,29 @@
         <f>'balance_raw_41792019'!$E$22</f>
         <v/>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" s="9">
+      <c r="F43" s="8">
+        <f>'balance_raw_41792019'!$F$22</f>
+        <v/>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" s="9">
         <f>IFERROR(B43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="H43" s="9">
+      <c r="I43" s="9">
         <f>IFERROR(C43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="I43" s="9">
+      <c r="J43" s="9">
         <f>IFERROR(D43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="J43" s="9">
+      <c r="K43" s="9">
         <f>IFERROR(E43/$B$43*100,"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="9">
+        <f>IFERROR(F43/$B$43*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2239,21 +2559,29 @@
         <f>'balance_raw_41792019'!$E$23</f>
         <v/>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" s="12">
+      <c r="F44" s="11">
+        <f>'balance_raw_41792019'!$F$23</f>
+        <v/>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" s="12">
         <f>IFERROR(B44/$B$44*100,"")</f>
         <v/>
       </c>
-      <c r="H44" s="12">
+      <c r="I44" s="12">
         <f>IFERROR(C44/$B$44*100,"")</f>
         <v/>
       </c>
-      <c r="I44" s="12">
+      <c r="J44" s="12">
         <f>IFERROR(D44/$B$44*100,"")</f>
         <v/>
       </c>
-      <c r="J44" s="12">
+      <c r="K44" s="12">
         <f>IFERROR(E44/$B$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="L44" s="12">
+        <f>IFERROR(F44/$B$44*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2279,21 +2607,29 @@
         <f>'balance_raw_41792019'!$E$24</f>
         <v/>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" s="9">
+      <c r="F45" s="8">
+        <f>'balance_raw_41792019'!$F$24</f>
+        <v/>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" s="9">
         <f>IFERROR(B45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="H45" s="9">
+      <c r="I45" s="9">
         <f>IFERROR(C45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="I45" s="9">
+      <c r="J45" s="9">
         <f>IFERROR(D45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="J45" s="9">
+      <c r="K45" s="9">
         <f>IFERROR(E45/$B$45*100,"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="9">
+        <f>IFERROR(F45/$B$45*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2319,21 +2655,29 @@
         <f>'balance_raw_41792019'!$E$25</f>
         <v/>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" s="6">
+      <c r="F46" s="5">
+        <f>'balance_raw_41792019'!$F$25</f>
+        <v/>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" s="6">
         <f>IFERROR(B46/$B$46*100,"")</f>
         <v/>
       </c>
-      <c r="H46" s="6">
+      <c r="I46" s="6">
         <f>IFERROR(C46/$B$46*100,"")</f>
         <v/>
       </c>
-      <c r="I46" s="6">
+      <c r="J46" s="6">
         <f>IFERROR(D46/$B$46*100,"")</f>
         <v/>
       </c>
-      <c r="J46" s="6">
+      <c r="K46" s="6">
         <f>IFERROR(E46/$B$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="6">
+        <f>IFERROR(F46/$B$46*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2359,21 +2703,29 @@
         <f>'balance_raw_41792019'!$E$26</f>
         <v/>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" s="12">
+      <c r="F47" s="11">
+        <f>'balance_raw_41792019'!$F$26</f>
+        <v/>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" s="12">
         <f>IFERROR(B47/$B$47*100,"")</f>
         <v/>
       </c>
-      <c r="H47" s="12">
+      <c r="I47" s="12">
         <f>IFERROR(C47/$B$47*100,"")</f>
         <v/>
       </c>
-      <c r="I47" s="12">
+      <c r="J47" s="12">
         <f>IFERROR(D47/$B$47*100,"")</f>
         <v/>
       </c>
-      <c r="J47" s="12">
+      <c r="K47" s="12">
         <f>IFERROR(E47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="12">
+        <f>IFERROR(F47/$B$47*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2399,21 +2751,29 @@
         <f>'balance_raw_41792019'!$E$27</f>
         <v/>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" s="12">
+      <c r="F48" s="11">
+        <f>'balance_raw_41792019'!$F$27</f>
+        <v/>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" s="12">
         <f>IFERROR(B48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="H48" s="12">
+      <c r="I48" s="12">
         <f>IFERROR(C48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="I48" s="12">
+      <c r="J48" s="12">
         <f>IFERROR(D48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="J48" s="12">
+      <c r="K48" s="12">
         <f>IFERROR(E48/$B$48*100,"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="12">
+        <f>IFERROR(F48/$B$48*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2435,18 +2795,24 @@
       <c r="E50" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" s="3" t="n">
+      <c r="F50" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="H50" s="3" t="n">
+      <c r="I50" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="J50" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="K50" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
@@ -2471,21 +2837,29 @@
         <f>'balance_raw_41792019'!$E$28</f>
         <v/>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" s="9">
+      <c r="F51" s="8">
+        <f>'balance_raw_41792019'!$F$28</f>
+        <v/>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" s="9">
         <f>IFERROR(B51/$B$51*100,"")</f>
         <v/>
       </c>
-      <c r="H51" s="9">
+      <c r="I51" s="9">
         <f>IFERROR(C51/$B$51*100,"")</f>
         <v/>
       </c>
-      <c r="I51" s="9">
+      <c r="J51" s="9">
         <f>IFERROR(D51/$B$51*100,"")</f>
         <v/>
       </c>
-      <c r="J51" s="9">
+      <c r="K51" s="9">
         <f>IFERROR(E51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="9">
+        <f>IFERROR(F51/$B$51*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2511,21 +2885,29 @@
         <f>'balance_raw_41792019'!$E$29</f>
         <v/>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" s="6">
+      <c r="F52" s="5">
+        <f>'balance_raw_41792019'!$F$29</f>
+        <v/>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" s="6">
         <f>IFERROR(B52/$B$52*100,"")</f>
         <v/>
       </c>
-      <c r="H52" s="6">
+      <c r="I52" s="6">
         <f>IFERROR(C52/$B$52*100,"")</f>
         <v/>
       </c>
-      <c r="I52" s="6">
+      <c r="J52" s="6">
         <f>IFERROR(D52/$B$52*100,"")</f>
         <v/>
       </c>
-      <c r="J52" s="6">
+      <c r="K52" s="6">
         <f>IFERROR(E52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="6">
+        <f>IFERROR(F52/$B$52*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2551,21 +2933,29 @@
         <f>'balance_raw_41792019'!$E$30</f>
         <v/>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" s="9">
+      <c r="F53" s="8">
+        <f>'balance_raw_41792019'!$F$30</f>
+        <v/>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" s="9">
         <f>IFERROR(B53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="H53" s="9">
+      <c r="I53" s="9">
         <f>IFERROR(C53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="I53" s="9">
+      <c r="J53" s="9">
         <f>IFERROR(D53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="J53" s="9">
+      <c r="K53" s="9">
         <f>IFERROR(E53/$B$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="9">
+        <f>IFERROR(F53/$B$53*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2591,21 +2981,29 @@
         <f>'balance_raw_41792019'!$E$31</f>
         <v/>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" s="6">
+      <c r="F54" s="5">
+        <f>'balance_raw_41792019'!$F$31</f>
+        <v/>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" s="6">
         <f>IFERROR(B54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="H54" s="6">
+      <c r="I54" s="6">
         <f>IFERROR(C54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="I54" s="6">
+      <c r="J54" s="6">
         <f>IFERROR(D54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="J54" s="6">
+      <c r="K54" s="6">
         <f>IFERROR(E54/$B$54*100,"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="6">
+        <f>IFERROR(F54/$B$54*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2631,21 +3029,29 @@
         <f>'balance_raw_41792019'!$E$32</f>
         <v/>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" s="9">
+      <c r="F55" s="8">
+        <f>'balance_raw_41792019'!$F$32</f>
+        <v/>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" s="9">
         <f>IFERROR(B55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="H55" s="9">
+      <c r="I55" s="9">
         <f>IFERROR(C55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="I55" s="9">
+      <c r="J55" s="9">
         <f>IFERROR(D55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="J55" s="9">
+      <c r="K55" s="9">
         <f>IFERROR(E55/$B$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="9">
+        <f>IFERROR(F55/$B$55*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2671,21 +3077,29 @@
         <f>'balance_raw_41792019'!$E$33</f>
         <v/>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" s="6">
+      <c r="F56" s="5">
+        <f>'balance_raw_41792019'!$F$33</f>
+        <v/>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" s="6">
         <f>IFERROR(B56/$B$56*100,"")</f>
         <v/>
       </c>
-      <c r="H56" s="6">
+      <c r="I56" s="6">
         <f>IFERROR(C56/$B$56*100,"")</f>
         <v/>
       </c>
-      <c r="I56" s="6">
+      <c r="J56" s="6">
         <f>IFERROR(D56/$B$56*100,"")</f>
         <v/>
       </c>
-      <c r="J56" s="6">
+      <c r="K56" s="6">
         <f>IFERROR(E56/$B$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="6">
+        <f>IFERROR(F56/$B$56*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2711,21 +3125,29 @@
         <f>'balance_raw_41792019'!$E$34</f>
         <v/>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" s="12">
+      <c r="F57" s="11">
+        <f>'balance_raw_41792019'!$F$34</f>
+        <v/>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" s="12">
         <f>IFERROR(B57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="H57" s="12">
+      <c r="I57" s="12">
         <f>IFERROR(C57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="I57" s="12">
+      <c r="J57" s="12">
         <f>IFERROR(D57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="J57" s="12">
+      <c r="K57" s="12">
         <f>IFERROR(E57/$B$57*100,"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="12">
+        <f>IFERROR(F57/$B$57*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2751,21 +3173,29 @@
         <f>'balance_raw_41792019'!$E$35</f>
         <v/>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" s="6">
+      <c r="F58" s="5">
+        <f>'balance_raw_41792019'!$F$35</f>
+        <v/>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" s="6">
         <f>IFERROR(B58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="H58" s="6">
+      <c r="I58" s="6">
         <f>IFERROR(C58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="I58" s="6">
+      <c r="J58" s="6">
         <f>IFERROR(D58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="J58" s="6">
+      <c r="K58" s="6">
         <f>IFERROR(E58/$B$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="6">
+        <f>IFERROR(F58/$B$58*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2791,21 +3221,29 @@
         <f>'balance_raw_41792019'!$E$36</f>
         <v/>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" s="12">
+      <c r="F59" s="11">
+        <f>'balance_raw_41792019'!$F$36</f>
+        <v/>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" s="12">
         <f>IFERROR(B59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="H59" s="12">
+      <c r="I59" s="12">
         <f>IFERROR(C59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="I59" s="12">
+      <c r="J59" s="12">
         <f>IFERROR(D59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="J59" s="12">
+      <c r="K59" s="12">
         <f>IFERROR(E59/$B$59*100,"")</f>
+        <v/>
+      </c>
+      <c r="L59" s="12">
+        <f>IFERROR(F59/$B$59*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2831,21 +3269,29 @@
         <f>'balance_raw_41792019'!$E$37</f>
         <v/>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" s="6">
+      <c r="F60" s="5">
+        <f>'balance_raw_41792019'!$F$37</f>
+        <v/>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" s="6">
         <f>IFERROR(B60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="H60" s="6">
+      <c r="I60" s="6">
         <f>IFERROR(C60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="I60" s="6">
+      <c r="J60" s="6">
         <f>IFERROR(D60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="J60" s="6">
+      <c r="K60" s="6">
         <f>IFERROR(E60/$B$60*100,"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="6">
+        <f>IFERROR(F60/$B$60*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2871,21 +3317,29 @@
         <f>'balance_raw_41792019'!$E$38</f>
         <v/>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" s="9">
+      <c r="F61" s="8">
+        <f>'balance_raw_41792019'!$F$38</f>
+        <v/>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" s="9">
         <f>IFERROR(B61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="H61" s="9">
+      <c r="I61" s="9">
         <f>IFERROR(C61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="I61" s="9">
+      <c r="J61" s="9">
         <f>IFERROR(D61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="J61" s="9">
+      <c r="K61" s="9">
         <f>IFERROR(E61/$B$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="L61" s="9">
+        <f>IFERROR(F61/$B$61*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2911,21 +3365,29 @@
         <f>'balance_raw_41792019'!$E$39</f>
         <v/>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" s="6">
+      <c r="F62" s="5">
+        <f>'balance_raw_41792019'!$F$39</f>
+        <v/>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" s="6">
         <f>IFERROR(B62/$B$62*100,"")</f>
         <v/>
       </c>
-      <c r="H62" s="6">
+      <c r="I62" s="6">
         <f>IFERROR(C62/$B$62*100,"")</f>
         <v/>
       </c>
-      <c r="I62" s="6">
+      <c r="J62" s="6">
         <f>IFERROR(D62/$B$62*100,"")</f>
         <v/>
       </c>
-      <c r="J62" s="6">
+      <c r="K62" s="6">
         <f>IFERROR(E62/$B$62*100,"")</f>
+        <v/>
+      </c>
+      <c r="L62" s="6">
+        <f>IFERROR(F62/$B$62*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2951,21 +3413,29 @@
         <f>'balance_raw_41792019'!$E$40</f>
         <v/>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" s="9">
+      <c r="F63" s="8">
+        <f>'balance_raw_41792019'!$F$40</f>
+        <v/>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" s="9">
         <f>IFERROR(B63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="H63" s="9">
+      <c r="I63" s="9">
         <f>IFERROR(C63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="I63" s="9">
+      <c r="J63" s="9">
         <f>IFERROR(D63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="J63" s="9">
+      <c r="K63" s="9">
         <f>IFERROR(E63/$B$63*100,"")</f>
+        <v/>
+      </c>
+      <c r="L63" s="9">
+        <f>IFERROR(F63/$B$63*100,"")</f>
         <v/>
       </c>
     </row>
@@ -2991,21 +3461,29 @@
         <f>'balance_raw_41792019'!$E$41</f>
         <v/>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" s="12">
+      <c r="F64" s="11">
+        <f>'balance_raw_41792019'!$F$41</f>
+        <v/>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" s="12">
         <f>IFERROR(B64/$B$64*100,"")</f>
         <v/>
       </c>
-      <c r="H64" s="12">
+      <c r="I64" s="12">
         <f>IFERROR(C64/$B$64*100,"")</f>
         <v/>
       </c>
-      <c r="I64" s="12">
+      <c r="J64" s="12">
         <f>IFERROR(D64/$B$64*100,"")</f>
         <v/>
       </c>
-      <c r="J64" s="12">
+      <c r="K64" s="12">
         <f>IFERROR(E64/$B$64*100,"")</f>
+        <v/>
+      </c>
+      <c r="L64" s="12">
+        <f>IFERROR(F64/$B$64*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3031,21 +3509,29 @@
         <f>'balance_raw_41792019'!$E$42</f>
         <v/>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" s="9">
+      <c r="F65" s="8">
+        <f>'balance_raw_41792019'!$F$42</f>
+        <v/>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" s="9">
         <f>IFERROR(B65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="H65" s="9">
+      <c r="I65" s="9">
         <f>IFERROR(C65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="I65" s="9">
+      <c r="J65" s="9">
         <f>IFERROR(D65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="J65" s="9">
+      <c r="K65" s="9">
         <f>IFERROR(E65/$B$65*100,"")</f>
+        <v/>
+      </c>
+      <c r="L65" s="9">
+        <f>IFERROR(F65/$B$65*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3071,21 +3557,29 @@
         <f>'balance_raw_41792019'!$E$43</f>
         <v/>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" s="6">
+      <c r="F66" s="5">
+        <f>'balance_raw_41792019'!$F$43</f>
+        <v/>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="6">
         <f>IFERROR(B66/$B$66*100,"")</f>
         <v/>
       </c>
-      <c r="H66" s="6">
+      <c r="I66" s="6">
         <f>IFERROR(C66/$B$66*100,"")</f>
         <v/>
       </c>
-      <c r="I66" s="6">
+      <c r="J66" s="6">
         <f>IFERROR(D66/$B$66*100,"")</f>
         <v/>
       </c>
-      <c r="J66" s="6">
+      <c r="K66" s="6">
         <f>IFERROR(E66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="6">
+        <f>IFERROR(F66/$B$66*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3111,21 +3605,29 @@
         <f>'balance_raw_41792019'!$E$44</f>
         <v/>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" s="9">
+      <c r="F67" s="8">
+        <f>'balance_raw_41792019'!$F$44</f>
+        <v/>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" s="9">
         <f>IFERROR(B67/$B$67*100,"")</f>
         <v/>
       </c>
-      <c r="H67" s="9">
+      <c r="I67" s="9">
         <f>IFERROR(C67/$B$67*100,"")</f>
         <v/>
       </c>
-      <c r="I67" s="9">
+      <c r="J67" s="9">
         <f>IFERROR(D67/$B$67*100,"")</f>
         <v/>
       </c>
-      <c r="J67" s="9">
+      <c r="K67" s="9">
         <f>IFERROR(E67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="9">
+        <f>IFERROR(F67/$B$67*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3151,21 +3653,29 @@
         <f>'balance_raw_41792019'!$E$45</f>
         <v/>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" s="6">
+      <c r="F68" s="5">
+        <f>'balance_raw_41792019'!$F$45</f>
+        <v/>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" s="6">
         <f>IFERROR(B68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="H68" s="6">
+      <c r="I68" s="6">
         <f>IFERROR(C68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="I68" s="6">
+      <c r="J68" s="6">
         <f>IFERROR(D68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="J68" s="6">
+      <c r="K68" s="6">
         <f>IFERROR(E68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="6">
+        <f>IFERROR(F68/$B$68*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3191,21 +3701,29 @@
         <f>'balance_raw_41792019'!$E$46</f>
         <v/>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" s="9">
+      <c r="F69" s="8">
+        <f>'balance_raw_41792019'!$F$46</f>
+        <v/>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" s="9">
         <f>IFERROR(B69/$B$69*100,"")</f>
         <v/>
       </c>
-      <c r="H69" s="9">
+      <c r="I69" s="9">
         <f>IFERROR(C69/$B$69*100,"")</f>
         <v/>
       </c>
-      <c r="I69" s="9">
+      <c r="J69" s="9">
         <f>IFERROR(D69/$B$69*100,"")</f>
         <v/>
       </c>
-      <c r="J69" s="9">
+      <c r="K69" s="9">
         <f>IFERROR(E69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="L69" s="9">
+        <f>IFERROR(F69/$B$69*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3231,21 +3749,29 @@
         <f>'balance_raw_41792019'!$E$47</f>
         <v/>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" s="6">
+      <c r="F70" s="5">
+        <f>'balance_raw_41792019'!$F$47</f>
+        <v/>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="6">
         <f>IFERROR(B70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="H70" s="6">
+      <c r="I70" s="6">
         <f>IFERROR(C70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="I70" s="6">
+      <c r="J70" s="6">
         <f>IFERROR(D70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="J70" s="6">
+      <c r="K70" s="6">
         <f>IFERROR(E70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="L70" s="6">
+        <f>IFERROR(F70/$B$70*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3271,21 +3797,29 @@
         <f>'balance_raw_41792019'!$E$48</f>
         <v/>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" s="9">
+      <c r="F71" s="8">
+        <f>'balance_raw_41792019'!$F$48</f>
+        <v/>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" s="9">
         <f>IFERROR(B71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="H71" s="9">
+      <c r="I71" s="9">
         <f>IFERROR(C71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="I71" s="9">
+      <c r="J71" s="9">
         <f>IFERROR(D71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="J71" s="9">
+      <c r="K71" s="9">
         <f>IFERROR(E71/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="L71" s="9">
+        <f>IFERROR(F71/$B$71*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3311,21 +3845,29 @@
         <f>'balance_raw_41792019'!$E$49</f>
         <v/>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" s="6">
+      <c r="F72" s="5">
+        <f>'balance_raw_41792019'!$F$49</f>
+        <v/>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" s="6">
         <f>IFERROR(B72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="H72" s="6">
+      <c r="I72" s="6">
         <f>IFERROR(C72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="I72" s="6">
+      <c r="J72" s="6">
         <f>IFERROR(D72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="J72" s="6">
+      <c r="K72" s="6">
         <f>IFERROR(E72/$B$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="L72" s="6">
+        <f>IFERROR(F72/$B$72*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3351,21 +3893,29 @@
         <f>'balance_raw_41792019'!$E$50</f>
         <v/>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" s="9">
+      <c r="F73" s="8">
+        <f>'balance_raw_41792019'!$F$50</f>
+        <v/>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="9">
         <f>IFERROR(B73/$B$73*100,"")</f>
         <v/>
       </c>
-      <c r="H73" s="9">
+      <c r="I73" s="9">
         <f>IFERROR(C73/$B$73*100,"")</f>
         <v/>
       </c>
-      <c r="I73" s="9">
+      <c r="J73" s="9">
         <f>IFERROR(D73/$B$73*100,"")</f>
         <v/>
       </c>
-      <c r="J73" s="9">
+      <c r="K73" s="9">
         <f>IFERROR(E73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="9">
+        <f>IFERROR(F73/$B$73*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3391,21 +3941,29 @@
         <f>'balance_raw_41792019'!$E$51</f>
         <v/>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" s="6">
+      <c r="F74" s="5">
+        <f>'balance_raw_41792019'!$F$51</f>
+        <v/>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="6">
         <f>IFERROR(B74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="H74" s="6">
+      <c r="I74" s="6">
         <f>IFERROR(C74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="I74" s="6">
+      <c r="J74" s="6">
         <f>IFERROR(D74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="J74" s="6">
+      <c r="K74" s="6">
         <f>IFERROR(E74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="6">
+        <f>IFERROR(F74/$B$74*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3431,21 +3989,29 @@
         <f>'balance_raw_41792019'!$E$52</f>
         <v/>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" s="9">
+      <c r="F75" s="8">
+        <f>'balance_raw_41792019'!$F$52</f>
+        <v/>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="9">
         <f>IFERROR(B75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="H75" s="9">
+      <c r="I75" s="9">
         <f>IFERROR(C75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="I75" s="9">
+      <c r="J75" s="9">
         <f>IFERROR(D75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="J75" s="9">
+      <c r="K75" s="9">
         <f>IFERROR(E75/$B$75*100,"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="9">
+        <f>IFERROR(F75/$B$75*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3471,21 +4037,29 @@
         <f>'balance_raw_41792019'!$E$53</f>
         <v/>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" s="12">
+      <c r="F76" s="11">
+        <f>'balance_raw_41792019'!$F$53</f>
+        <v/>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" s="12">
         <f>IFERROR(B76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="H76" s="12">
+      <c r="I76" s="12">
         <f>IFERROR(C76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="I76" s="12">
+      <c r="J76" s="12">
         <f>IFERROR(D76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="J76" s="12">
+      <c r="K76" s="12">
         <f>IFERROR(E76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="L76" s="12">
+        <f>IFERROR(F76/$B$76*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3511,21 +4085,29 @@
         <f>'balance_raw_41792019'!$E$54</f>
         <v/>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" s="12">
+      <c r="F77" s="11">
+        <f>'balance_raw_41792019'!$F$54</f>
+        <v/>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="12">
         <f>IFERROR(B77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="H77" s="12">
+      <c r="I77" s="12">
         <f>IFERROR(C77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="I77" s="12">
+      <c r="J77" s="12">
         <f>IFERROR(D77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="J77" s="12">
+      <c r="K77" s="12">
         <f>IFERROR(E77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="12">
+        <f>IFERROR(F77/$B$77*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3551,21 +4133,29 @@
         <f>'balance_raw_41792019'!$E$55</f>
         <v/>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" s="12">
+      <c r="F78" s="11">
+        <f>'balance_raw_41792019'!$F$55</f>
+        <v/>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" s="12">
         <f>IFERROR(B78/$B$78*100,"")</f>
         <v/>
       </c>
-      <c r="H78" s="12">
+      <c r="I78" s="12">
         <f>IFERROR(C78/$B$78*100,"")</f>
         <v/>
       </c>
-      <c r="I78" s="12">
+      <c r="J78" s="12">
         <f>IFERROR(D78/$B$78*100,"")</f>
         <v/>
       </c>
-      <c r="J78" s="12">
+      <c r="K78" s="12">
         <f>IFERROR(E78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="L78" s="12">
+        <f>IFERROR(F78/$B$78*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3587,6 +4177,9 @@
       <c r="E80" s="3" t="n">
         <v>2024</v>
       </c>
+      <c r="F80" s="3" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -3610,21 +4203,29 @@
         <f>'res_raw_41792019'!$E$19</f>
         <v/>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" s="9">
+      <c r="F81" s="8">
+        <f>'res_raw_41792019'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" s="9">
         <f>IFERROR(B81/$B$81*100,"")</f>
         <v/>
       </c>
-      <c r="H81" s="9">
+      <c r="I81" s="9">
         <f>IFERROR(C81/$B$81*100,"")</f>
         <v/>
       </c>
-      <c r="I81" s="9">
+      <c r="J81" s="9">
         <f>IFERROR(D81/$B$81*100,"")</f>
         <v/>
       </c>
-      <c r="J81" s="9">
+      <c r="K81" s="9">
         <f>IFERROR(E81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="L81" s="9">
+        <f>IFERROR(F81/$B$81*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3650,21 +4251,29 @@
         <f>'res_raw_41792019'!$E$20</f>
         <v/>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" s="6">
+      <c r="F82" s="5">
+        <f>'res_raw_41792019'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" s="6">
         <f>IFERROR(B82/$B$82*100,"")</f>
         <v/>
       </c>
-      <c r="H82" s="6">
+      <c r="I82" s="6">
         <f>IFERROR(C82/$B$82*100,"")</f>
         <v/>
       </c>
-      <c r="I82" s="6">
+      <c r="J82" s="6">
         <f>IFERROR(D82/$B$82*100,"")</f>
         <v/>
       </c>
-      <c r="J82" s="6">
+      <c r="K82" s="6">
         <f>IFERROR(E82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="L82" s="6">
+        <f>IFERROR(F82/$B$82*100,"")</f>
         <v/>
       </c>
     </row>
@@ -3686,6 +4295,9 @@
       <c r="E84" s="3" t="n">
         <v>2024</v>
       </c>
+      <c r="F84" s="3" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -3709,6 +4321,10 @@
         <f>IFERROR(($E$13+$E$15+$E$14)/$E$48*100,"")</f>
         <v/>
       </c>
+      <c r="F85" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$48*100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
@@ -3732,6 +4348,10 @@
         <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
         <v/>
       </c>
+      <c r="F86" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -3755,6 +4375,10 @@
         <f>IFERROR($E$4/$E$48,"")</f>
         <v/>
       </c>
+      <c r="F87" s="13">
+        <f>IFERROR($F$4/$F$48,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -3778,6 +4402,10 @@
         <f>IFERROR($E$18/$E$57*100,"")</f>
         <v/>
       </c>
+      <c r="F88" s="14">
+        <f>IFERROR($F$18/$F$57*100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -3801,6 +4429,10 @@
         <f>IFERROR($E$16/($E$78-$E$57)*100,"")</f>
         <v/>
       </c>
+      <c r="F89" s="13">
+        <f>IFERROR($F$16/($F$78-$F$57)*100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -3824,6 +4456,10 @@
         <f>IFERROR($E$57/$E$48*100,"")</f>
         <v/>
       </c>
+      <c r="F90" s="14">
+        <f>IFERROR($F$57/$F$48*100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -3847,6 +4483,10 @@
         <f>IFERROR(($E$78-$E$57)/$E$57,"")</f>
         <v/>
       </c>
+      <c r="F91" s="13">
+        <f>IFERROR(($F$78-$F$57)/$F$57,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -3870,6 +4510,10 @@
         <f>IFERROR($E$47/$E$76*100,"")</f>
         <v/>
       </c>
+      <c r="F92" s="14">
+        <f>IFERROR($F$47/$F$76*100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -3893,6 +4537,10 @@
         <f>IFERROR(E85-E89,"")</f>
         <v/>
       </c>
+      <c r="F93" s="13">
+        <f>IFERROR(F85-F89,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -3916,6 +4564,10 @@
         <f>IFERROR(($E$78-$E$57)/$E$48*100,"")</f>
         <v/>
       </c>
+      <c r="F94" s="14">
+        <f>IFERROR(($F$78-$F$57)/$F$48*100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -3938,6 +4590,17 @@
       <c r="E95" s="13">
         <f>IFERROR($E$36/($E$57+$E$64)*100,"")</f>
         <v/>
+      </c>
+      <c r="F95" s="13">
+        <f>IFERROR($F$36/($F$57+$F$64)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3951,7 +4614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -3959,6 +4622,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3979,6 +4643,9 @@
       <c r="E1" s="3" t="n">
         <v>2024</v>
       </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -3998,6 +4665,9 @@
       <c r="E2" s="16" t="n">
         <v>1180450</v>
       </c>
+      <c r="F2" s="16" t="n">
+        <v>1254967</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -4017,6 +4687,7 @@
       <c r="E3" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F3" s="16" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -4036,6 +4707,9 @@
       <c r="E4" s="16" t="n">
         <v>1101834</v>
       </c>
+      <c r="F4" s="16" t="n">
+        <v>1190226</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -4055,6 +4729,9 @@
       <c r="E5" s="16" t="n">
         <v>32054</v>
       </c>
+      <c r="F5" s="16" t="n">
+        <v>43465</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -4074,6 +4751,9 @@
       <c r="E6" s="16" t="n">
         <v>46562</v>
       </c>
+      <c r="F6" s="16" t="n">
+        <v>21276</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -4093,6 +4773,9 @@
       <c r="E7" s="16" t="n">
         <v>37443</v>
       </c>
+      <c r="F7" s="16" t="n">
+        <v>32577</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
@@ -4118,6 +4801,9 @@
       </c>
       <c r="E9" s="16" t="n">
         <v>3677</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>4333</v>
       </c>
     </row>
     <row r="10">
@@ -4130,6 +4816,7 @@
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -4149,6 +4836,9 @@
       <c r="E11" s="16" t="n">
         <v>5442</v>
       </c>
+      <c r="F11" s="16" t="n">
+        <v>-15634</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -4168,6 +4858,9 @@
       <c r="E12" s="16" t="n">
         <v>25090</v>
       </c>
+      <c r="F12" s="16" t="n">
+        <v>26055</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -4187,6 +4880,9 @@
       <c r="E13" s="16" t="n">
         <v>6827</v>
       </c>
+      <c r="F13" s="16" t="n">
+        <v>3538</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -4205,6 +4901,9 @@
       </c>
       <c r="E14" s="16" t="n">
         <v>3102</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>4285</v>
       </c>
     </row>
     <row r="15">
@@ -4219,6 +4918,9 @@
       <c r="E15" s="16" t="n">
         <v>-29476</v>
       </c>
+      <c r="F15" s="16" t="n">
+        <v>26012</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4238,6 +4940,9 @@
       <c r="E16" s="16" t="n">
         <v>34918</v>
       </c>
+      <c r="F16" s="16" t="n">
+        <v>10378</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -4257,6 +4962,9 @@
       <c r="E17" s="16" t="n">
         <v>2202</v>
       </c>
+      <c r="F17" s="16" t="n">
+        <v>-3405</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -4276,6 +4984,9 @@
       <c r="E18" s="16" t="n">
         <v>32716</v>
       </c>
+      <c r="F18" s="16" t="n">
+        <v>13783</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -4295,6 +5006,9 @@
       <c r="E19" s="16" t="n">
         <v>107</v>
       </c>
+      <c r="F19" s="16" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -4313,6 +5027,9 @@
       </c>
       <c r="E20" s="16" t="n">
         <v>310</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4326,7 +5043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4334,6 +5051,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4354,6 +5072,9 @@
       <c r="E1" s="3" t="n">
         <v>2024</v>
       </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -4365,6 +5086,7 @@
       <c r="C2" s="16" t="n"/>
       <c r="D2" s="16" t="n"/>
       <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -4376,6 +5098,7 @@
       <c r="C3" s="16" t="n"/>
       <c r="D3" s="16" t="n"/>
       <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -4395,6 +5118,9 @@
       <c r="E4" s="16" t="n">
         <v>12191</v>
       </c>
+      <c r="F4" s="16" t="n">
+        <v>10111</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
@@ -4413,6 +5139,9 @@
       </c>
       <c r="E5" s="16" t="n">
         <v>18171</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>20878</v>
       </c>
     </row>
     <row r="6">
@@ -4425,6 +5154,7 @@
       <c r="C6" s="16" t="n"/>
       <c r="D6" s="16" t="n"/>
       <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -4436,6 +5166,7 @@
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -4454,6 +5185,9 @@
       </c>
       <c r="E8" s="16" t="n">
         <v>476</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -4466,6 +5200,7 @@
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="16" t="n"/>
       <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -4477,6 +5212,7 @@
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -4496,6 +5232,9 @@
       <c r="E11" s="16" t="n">
         <v>476</v>
       </c>
+      <c r="F11" s="16" t="n">
+        <v>468</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -4514,6 +5253,9 @@
       </c>
       <c r="E12" s="16" t="n">
         <v>58609</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>70652</v>
       </c>
     </row>
     <row r="13">
@@ -4526,6 +5268,7 @@
       <c r="C13" s="16" t="n"/>
       <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -4545,6 +5288,9 @@
       <c r="E14" s="16" t="n">
         <v>58609</v>
       </c>
+      <c r="F14" s="16" t="n">
+        <v>70652</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -4564,6 +5310,9 @@
       <c r="E15" s="16" t="n">
         <v>77256</v>
       </c>
+      <c r="F15" s="16" t="n">
+        <v>91998</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -4583,6 +5332,9 @@
       <c r="E16" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" s="16" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -4602,6 +5354,9 @@
       <c r="E17" s="16" t="n">
         <v>29081</v>
       </c>
+      <c r="F17" s="16" t="n">
+        <v>2445</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -4621,6 +5376,9 @@
       <c r="E18" s="16" t="n">
         <v>12054</v>
       </c>
+      <c r="F18" s="16" t="n">
+        <v>11869</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -4640,6 +5398,9 @@
       <c r="E19" s="16" t="n">
         <v>56986</v>
       </c>
+      <c r="F19" s="16" t="n">
+        <v>67950</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -4655,6 +5416,7 @@
       </c>
       <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -4666,6 +5428,9 @@
       <c r="C21" s="16" t="n"/>
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n">
+        <v>3028</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -4681,6 +5446,7 @@
       </c>
       <c r="D22" s="16" t="n"/>
       <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
@@ -4700,6 +5466,9 @@
       <c r="E23" s="16" t="n">
         <v>98121</v>
       </c>
+      <c r="F23" s="16" t="n">
+        <v>85448</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -4717,6 +5486,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
@@ -4736,6 +5506,9 @@
       <c r="E25" s="16" t="n">
         <v>173721</v>
       </c>
+      <c r="F25" s="16" t="n">
+        <v>178777</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
@@ -4755,6 +5528,9 @@
       <c r="E26" s="16" t="n">
         <v>271842</v>
       </c>
+      <c r="F26" s="16" t="n">
+        <v>264225</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
@@ -4774,6 +5550,9 @@
       <c r="E27" s="16" t="n">
         <v>349098</v>
       </c>
+      <c r="F27" s="16" t="n">
+        <v>356223</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -4793,6 +5572,9 @@
       <c r="E28" s="16" t="n">
         <v>11939</v>
       </c>
+      <c r="F28" s="16" t="n">
+        <v>11939</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
@@ -4811,6 +5593,9 @@
       </c>
       <c r="E29" s="16" t="n">
         <v>29717</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>56760</v>
       </c>
     </row>
     <row r="30">
@@ -4823,6 +5608,7 @@
       <c r="C30" s="16" t="n"/>
       <c r="D30" s="16" t="n"/>
       <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -4838,6 +5624,9 @@
       <c r="E31" s="16" t="n">
         <v>321</v>
       </c>
+      <c r="F31" s="16" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
@@ -4849,6 +5638,7 @@
       <c r="C32" s="16" t="n"/>
       <c r="D32" s="16" t="n"/>
       <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
@@ -4868,6 +5658,9 @@
       <c r="E33" s="16" t="n">
         <v>34575</v>
       </c>
+      <c r="F33" s="16" t="n">
+        <v>22303</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -4887,6 +5680,9 @@
       <c r="E34" s="16" t="n">
         <v>106552</v>
       </c>
+      <c r="F34" s="16" t="n">
+        <v>91052</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
@@ -4906,6 +5702,9 @@
       <c r="E35" s="16" t="n">
         <v>2104</v>
       </c>
+      <c r="F35" s="16" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -4925,6 +5724,9 @@
       <c r="E36" s="16" t="n">
         <v>2104</v>
       </c>
+      <c r="F36" s="16" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
@@ -4940,6 +5742,7 @@
       </c>
       <c r="D37" s="16" t="n"/>
       <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
@@ -4951,6 +5754,7 @@
       <c r="C38" s="16" t="n"/>
       <c r="D38" s="16" t="n"/>
       <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
@@ -4962,6 +5766,7 @@
       <c r="C39" s="16" t="n"/>
       <c r="D39" s="16" t="n"/>
       <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
@@ -4973,6 +5778,7 @@
       <c r="C40" s="16" t="n"/>
       <c r="D40" s="16" t="n"/>
       <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
@@ -4988,6 +5794,7 @@
       </c>
       <c r="D41" s="16" t="n"/>
       <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
@@ -4999,6 +5806,7 @@
       <c r="C42" s="16" t="n"/>
       <c r="D42" s="16" t="n"/>
       <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
@@ -5010,6 +5818,7 @@
       <c r="C43" s="16" t="n"/>
       <c r="D43" s="16" t="n"/>
       <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
@@ -5028,6 +5837,9 @@
       </c>
       <c r="E44" s="16" t="n">
         <v>356</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>834</v>
       </c>
     </row>
     <row r="45">
@@ -5040,6 +5852,7 @@
       <c r="C45" s="16" t="n"/>
       <c r="D45" s="16" t="n"/>
       <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
@@ -5059,6 +5872,9 @@
       <c r="E46" s="16" t="n">
         <v>33503</v>
       </c>
+      <c r="F46" s="16" t="n">
+        <v>42021</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
@@ -5078,6 +5894,9 @@
       <c r="E47" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F47" s="16" t="n">
+        <v>10831</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
@@ -5095,6 +5914,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
@@ -5113,6 +5933,9 @@
       </c>
       <c r="E49" s="16" t="n">
         <v>2319</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5125,6 +5948,7 @@
       <c r="C50" s="16" t="n"/>
       <c r="D50" s="16" t="n"/>
       <c r="E50" s="16" t="n"/>
+      <c r="F50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
@@ -5144,6 +5968,9 @@
       <c r="E51" s="16" t="n">
         <v>8222</v>
       </c>
+      <c r="F51" s="16" t="n">
+        <v>7567</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
@@ -5163,6 +5990,9 @@
       <c r="E52" s="16" t="n">
         <v>196042</v>
       </c>
+      <c r="F52" s="16" t="n">
+        <v>202314</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -5182,6 +6012,9 @@
       <c r="E53" s="16" t="n">
         <v>240442</v>
       </c>
+      <c r="F53" s="16" t="n">
+        <v>263567</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -5201,6 +6034,9 @@
       <c r="E54" s="16" t="n">
         <v>240442</v>
       </c>
+      <c r="F54" s="16" t="n">
+        <v>263567</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -5219,6 +6055,9 @@
       </c>
       <c r="E55" s="16" t="n">
         <v>349098</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>356223</v>
       </c>
     </row>
   </sheetData>
@@ -5257,13 +6096,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -5289,15 +6128,15 @@
         </is>
       </c>
       <c r="B5" s="24">
+        <f>'res_raw_41792019'!$F$2</f>
+        <v/>
+      </c>
+      <c r="C5" s="24">
         <f>'res_raw_41792019'!$E$2</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="D5" s="24">
         <f>'res_raw_41792019'!$D$2</f>
-        <v/>
-      </c>
-      <c r="D5" s="24">
-        <f>'res_raw_41792019'!$C$2</f>
         <v/>
       </c>
       <c r="F5" s="25" t="inlineStr">
@@ -5313,15 +6152,15 @@
         </is>
       </c>
       <c r="B6" s="24">
+        <f>'res_raw_41792019'!$F$3</f>
+        <v/>
+      </c>
+      <c r="C6" s="24">
         <f>'res_raw_41792019'!$E$3</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="D6" s="24">
         <f>'res_raw_41792019'!$D$3</f>
-        <v/>
-      </c>
-      <c r="D6" s="24">
-        <f>'res_raw_41792019'!$C$3</f>
         <v/>
       </c>
       <c r="F6" s="25" t="inlineStr">
@@ -5337,15 +6176,15 @@
         </is>
       </c>
       <c r="B7" s="24">
+        <f>-'res_raw_41792019'!$F$4</f>
+        <v/>
+      </c>
+      <c r="C7" s="24">
         <f>-'res_raw_41792019'!$E$4</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="D7" s="24">
         <f>-'res_raw_41792019'!$D$4</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>-'res_raw_41792019'!$C$4</f>
         <v/>
       </c>
       <c r="F7" s="25" t="inlineStr">
@@ -5361,15 +6200,15 @@
         </is>
       </c>
       <c r="B8" s="24">
+        <f>-'res_raw_41792019'!$F$5</f>
+        <v/>
+      </c>
+      <c r="C8" s="24">
         <f>-'res_raw_41792019'!$E$5</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="D8" s="24">
         <f>-'res_raw_41792019'!$D$5</f>
-        <v/>
-      </c>
-      <c r="D8" s="24">
-        <f>-'res_raw_41792019'!$C$5</f>
         <v/>
       </c>
       <c r="F8" s="25" t="inlineStr">
@@ -5409,15 +6248,15 @@
         </is>
       </c>
       <c r="B10" s="24">
+        <f>-'res_raw_41792019'!$F$7</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
         <f>-'res_raw_41792019'!$E$7</f>
         <v/>
       </c>
-      <c r="C10" s="24">
+      <c r="D10" s="24">
         <f>-'res_raw_41792019'!$D$7</f>
-        <v/>
-      </c>
-      <c r="D10" s="24">
-        <f>-'res_raw_41792019'!$C$7</f>
         <v/>
       </c>
       <c r="F10" s="25" t="inlineStr">
@@ -5433,15 +6272,15 @@
         </is>
       </c>
       <c r="B11" s="24">
+        <f>-'res_raw_41792019'!$F$9</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
         <f>-'res_raw_41792019'!$E$9</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="D11" s="24">
         <f>-'res_raw_41792019'!$D$9</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>-'res_raw_41792019'!$C$9</f>
         <v/>
       </c>
       <c r="F11" s="25" t="inlineStr">
@@ -5457,15 +6296,15 @@
         </is>
       </c>
       <c r="B12" s="24">
+        <f>-'res_raw_41792019'!$F$10</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
         <f>-'res_raw_41792019'!$E$10</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="D12" s="24">
         <f>-'res_raw_41792019'!$D$10</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>-'res_raw_41792019'!$C$10</f>
         <v/>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -5505,15 +6344,15 @@
         </is>
       </c>
       <c r="B14" s="24">
+        <f>N('res_raw_41792019'!$F$12)+N('res_raw_41792019'!$F$13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
         <f>N('res_raw_41792019'!$E$12)+N('res_raw_41792019'!$E$13)</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="D14" s="24">
         <f>N('res_raw_41792019'!$D$12)+N('res_raw_41792019'!$D$13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>N('res_raw_41792019'!$C$12)+N('res_raw_41792019'!$C$13)</f>
         <v/>
       </c>
       <c r="F14" s="25" t="inlineStr">
@@ -5529,15 +6368,15 @@
         </is>
       </c>
       <c r="B15" s="24">
+        <f>-'res_raw_41792019'!$F$14</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
         <f>-'res_raw_41792019'!$E$14</f>
         <v/>
       </c>
-      <c r="C15" s="24">
+      <c r="D15" s="24">
         <f>-'res_raw_41792019'!$D$14</f>
-        <v/>
-      </c>
-      <c r="D15" s="24">
-        <f>-'res_raw_41792019'!$C$14</f>
         <v/>
       </c>
       <c r="F15" s="25" t="inlineStr">
@@ -5595,15 +6434,15 @@
         </is>
       </c>
       <c r="B19" s="24">
+        <f>'balance_raw_41792019'!$F$15</f>
+        <v/>
+      </c>
+      <c r="C19" s="24">
         <f>'balance_raw_41792019'!$E$15</f>
         <v/>
       </c>
-      <c r="C19" s="24">
+      <c r="D19" s="24">
         <f>'balance_raw_41792019'!$D$15</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>'balance_raw_41792019'!$C$15</f>
         <v/>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -5619,15 +6458,15 @@
         </is>
       </c>
       <c r="B20" s="24">
+        <f>'balance_raw_41792019'!$F$26</f>
+        <v/>
+      </c>
+      <c r="C20" s="24">
         <f>'balance_raw_41792019'!$E$26</f>
         <v/>
       </c>
-      <c r="C20" s="24">
+      <c r="D20" s="24">
         <f>'balance_raw_41792019'!$D$26</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>'balance_raw_41792019'!$C$26</f>
         <v/>
       </c>
       <c r="F20" s="25" t="inlineStr">
@@ -5674,15 +6513,15 @@
         </is>
       </c>
       <c r="B23" s="24">
+        <f>'balance_raw_41792019'!$F$34</f>
+        <v/>
+      </c>
+      <c r="C23" s="24">
         <f>'balance_raw_41792019'!$E$34</f>
         <v/>
       </c>
-      <c r="C23" s="24">
+      <c r="D23" s="24">
         <f>'balance_raw_41792019'!$D$34</f>
-        <v/>
-      </c>
-      <c r="D23" s="24">
-        <f>'balance_raw_41792019'!$C$34</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -5698,15 +6537,15 @@
         </is>
       </c>
       <c r="B24" s="24">
+        <f>'balance_raw_41792019'!$F$55-'balance_raw_41792019'!$F$34</f>
+        <v/>
+      </c>
+      <c r="C24" s="24">
         <f>'balance_raw_41792019'!$E$55-'balance_raw_41792019'!$E$34</f>
         <v/>
       </c>
-      <c r="C24" s="24">
+      <c r="D24" s="24">
         <f>'balance_raw_41792019'!$D$55-'balance_raw_41792019'!$D$34</f>
-        <v/>
-      </c>
-      <c r="D24" s="24">
-        <f>'balance_raw_41792019'!$C$55-'balance_raw_41792019'!$C$34</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -5779,15 +6618,15 @@
         </is>
       </c>
       <c r="B29" s="24">
+        <f>'balance_raw_41792019'!$F$16</f>
+        <v/>
+      </c>
+      <c r="C29" s="24">
         <f>'balance_raw_41792019'!$E$16</f>
         <v/>
       </c>
-      <c r="C29" s="24">
+      <c r="D29" s="24">
         <f>'balance_raw_41792019'!$D$16</f>
-        <v/>
-      </c>
-      <c r="D29" s="24">
-        <f>'balance_raw_41792019'!$C$16</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -5803,15 +6642,15 @@
         </is>
       </c>
       <c r="B30" s="24">
+        <f>'balance_raw_41792019'!$F$53</f>
+        <v/>
+      </c>
+      <c r="C30" s="24">
         <f>'balance_raw_41792019'!$E$53</f>
         <v/>
       </c>
-      <c r="C30" s="24">
+      <c r="D30" s="24">
         <f>'balance_raw_41792019'!$D$53</f>
-        <v/>
-      </c>
-      <c r="D30" s="24">
-        <f>'balance_raw_41792019'!$C$53</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -5968,7 +6807,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6086,7 +6925,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6262,7 +7101,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -6295,15 +7134,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_41792019'!$E$27="","—",IF(ABS(B21-'balance_raw_41792019'!$E$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_41792019'!$E$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_41792019'!$F$27="","—",IF(ABS(B21-'balance_raw_41792019'!$F$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_41792019'!$F$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_41792019'!$D$27="","—",IF(ABS(C21-'balance_raw_41792019'!$D$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_41792019'!$D$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_41792019'!$E$27="","—",IF(ABS(C21-'balance_raw_41792019'!$E$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_41792019'!$E$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_41792019'!$C$27="","—",IF(ABS(D21-'balance_raw_41792019'!$C$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_41792019'!$C$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_41792019'!$D$27="","—",IF(ABS(D21-'balance_raw_41792019'!$D$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_41792019'!$D$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6319,15 +7158,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_41792019'!$E$55="","—",IF(ABS(B25-'balance_raw_41792019'!$E$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_41792019'!$E$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_41792019'!$F$55="","—",IF(ABS(B25-'balance_raw_41792019'!$F$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_41792019'!$F$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_41792019'!$D$55="","—",IF(ABS(C25-'balance_raw_41792019'!$D$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_41792019'!$D$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_41792019'!$E$55="","—",IF(ABS(C25-'balance_raw_41792019'!$E$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_41792019'!$E$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_41792019'!$C$55="","—",IF(ABS(D25-'balance_raw_41792019'!$C$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_41792019'!$C$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_41792019'!$D$55="","—",IF(ABS(D25-'balance_raw_41792019'!$D$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_41792019'!$D$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -6367,15 +7206,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw_41792019'!$E$6="","—",IF(ABS(B9-'res_raw_41792019'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw_41792019'!$E$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$F$6="","—",IF(ABS(B9-'res_raw_41792019'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw_41792019'!$F$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw_41792019'!$D$6="","—",IF(ABS(C9-'res_raw_41792019'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw_41792019'!$D$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$E$6="","—",IF(ABS(C9-'res_raw_41792019'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw_41792019'!$E$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw_41792019'!$C$6="","—",IF(ABS(D9-'res_raw_41792019'!$C$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw_41792019'!$C$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$D$6="","—",IF(ABS(D9-'res_raw_41792019'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw_41792019'!$D$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -6391,15 +7230,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw_41792019'!$E$11="","—",IF(ABS(B13-'res_raw_41792019'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_41792019'!$E$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$F$11="","—",IF(ABS(B13-'res_raw_41792019'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_41792019'!$F$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw_41792019'!$D$11="","—",IF(ABS(C13-'res_raw_41792019'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_41792019'!$D$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$E$11="","—",IF(ABS(C13-'res_raw_41792019'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_41792019'!$E$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw_41792019'!$C$11="","—",IF(ABS(D13-'res_raw_41792019'!$C$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_41792019'!$C$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$D$11="","—",IF(ABS(D13-'res_raw_41792019'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_41792019'!$D$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">
@@ -6415,15 +7254,15 @@
         </is>
       </c>
       <c r="B66" s="29">
-        <f>IF('res_raw_41792019'!$E$16="","—",IF(ABS(B16-'res_raw_41792019'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_41792019'!$E$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$F$16="","—",IF(ABS(B16-'res_raw_41792019'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_41792019'!$F$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C66" s="29">
-        <f>IF('res_raw_41792019'!$D$16="","—",IF(ABS(C16-'res_raw_41792019'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_41792019'!$D$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$E$16="","—",IF(ABS(C16-'res_raw_41792019'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_41792019'!$E$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D66" s="29">
-        <f>IF('res_raw_41792019'!$C$16="","—",IF(ABS(D16-'res_raw_41792019'!$C$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_41792019'!$C$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_41792019'!$D$16="","—",IF(ABS(D16-'res_raw_41792019'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_41792019'!$D$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F66" s="25" t="inlineStr">
